--- a/event_registration_forms/028_cultural_event_vendor_check_out_form--event_registration_forms.xlsx
+++ b/event_registration_forms/028_cultural_event_vendor_check_out_form--event_registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -780,8 +780,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -809,12 +809,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'30_days',_'value':_30}</t>
+          <t>30_days</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': '30 days', 'value': 30}</t>
+          <t>30 days</t>
         </is>
       </c>
     </row>
@@ -826,12 +826,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'60_days',_'value':_60}</t>
+          <t>60_days</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': '60 days', 'value': 60}</t>
+          <t>60 days</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'net_30',_'value':_'net_30'}</t>
+          <t>net_30</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Net 30', 'value': 'net_30'}</t>
+          <t>Net 30</t>
         </is>
       </c>
     </row>
@@ -860,12 +860,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'net_60',_'value':_'net_60'}</t>
+          <t>net_60</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Net 60', 'value': 'net_60'}</t>
+          <t>Net 60</t>
         </is>
       </c>
     </row>
@@ -877,12 +877,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'bank_draft',_'value':_'bank_draft'}</t>
+          <t>bank_draft</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Bank Draft', 'value': 'bank_draft'}</t>
+          <t>Bank Draft</t>
         </is>
       </c>
     </row>
@@ -894,12 +894,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'certified_check',_'value':_'certified_check'}</t>
+          <t>certified_check</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Certified Check', 'value': 'certified_check'}</t>
+          <t>Certified Check</t>
         </is>
       </c>
     </row>
@@ -911,12 +911,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'credit_card',_'value':_'credit_card'}</t>
+          <t>credit_card</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Credit Card', 'value': 'credit_card'}</t>
+          <t>Credit Card</t>
         </is>
       </c>
     </row>
@@ -928,12 +928,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'pay_pal',_'value':_'paypal'}</t>
+          <t>pay_pal</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Pay Pal', 'value': 'paypal'}</t>
+          <t>Pay Pal</t>
         </is>
       </c>
     </row>
@@ -945,12 +945,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'not_paid',_'value':_'not_paid'}</t>
+          <t>not_paid</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Not Paid', 'value': 'not_paid'}</t>
+          <t>Not Paid</t>
         </is>
       </c>
     </row>
@@ -962,12 +962,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'paid',_'value':_'paid'}</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Paid', 'value': 'paid'}</t>
+          <t>Paid</t>
         </is>
       </c>
     </row>
@@ -979,12 +979,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'partially_paid',_'value':_'partially_paid'}</t>
+          <t>partially_paid</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Partially Paid', 'value': 'partially_paid'}</t>
+          <t>Partially Paid</t>
         </is>
       </c>
     </row>
